--- a/data/nzd0507/nzd0507.xlsx
+++ b/data/nzd0507/nzd0507.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I335"/>
+  <dimension ref="A1:I338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11493,6 +11493,105 @@
         <v>351.11</v>
       </c>
       <c r="I335" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>333.48</v>
+      </c>
+      <c r="C336" t="n">
+        <v>333.48</v>
+      </c>
+      <c r="D336" t="n">
+        <v>333.81</v>
+      </c>
+      <c r="E336" t="n">
+        <v>350.9</v>
+      </c>
+      <c r="F336" t="n">
+        <v>345.94</v>
+      </c>
+      <c r="G336" t="n">
+        <v>339.63</v>
+      </c>
+      <c r="H336" t="n">
+        <v>351.65</v>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>335.34</v>
+      </c>
+      <c r="C337" t="n">
+        <v>334.8</v>
+      </c>
+      <c r="D337" t="n">
+        <v>334.61</v>
+      </c>
+      <c r="E337" t="n">
+        <v>351.5</v>
+      </c>
+      <c r="F337" t="n">
+        <v>346.79</v>
+      </c>
+      <c r="G337" t="n">
+        <v>340.35</v>
+      </c>
+      <c r="H337" t="n">
+        <v>352.64</v>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>334.78</v>
+      </c>
+      <c r="C338" t="n">
+        <v>334.3</v>
+      </c>
+      <c r="D338" t="n">
+        <v>333</v>
+      </c>
+      <c r="E338" t="n">
+        <v>350.77</v>
+      </c>
+      <c r="F338" t="n">
+        <v>346.19</v>
+      </c>
+      <c r="G338" t="n">
+        <v>338.7</v>
+      </c>
+      <c r="H338" t="n">
+        <v>352.14</v>
+      </c>
+      <c r="I338" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11509,7 +11608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B353"/>
+  <dimension ref="A1:B356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15042,6 +15141,36 @@
       </c>
       <c r="B353" t="n">
         <v>-0.75</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>0.23</v>
       </c>
     </row>
   </sheetData>
@@ -15210,28 +15339,28 @@
         <v>0.082</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02964200893588213</v>
+        <v>-0.02575194040913379</v>
       </c>
       <c r="J2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K2" t="n">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008486028710730231</v>
+        <v>0.0006514918946389781</v>
       </c>
       <c r="M2" t="n">
-        <v>5.760767136864588</v>
+        <v>5.727976413356041</v>
       </c>
       <c r="N2" t="n">
-        <v>53.96818874844162</v>
+        <v>53.53611833038721</v>
       </c>
       <c r="O2" t="n">
-        <v>7.346304427972041</v>
+        <v>7.316838000829812</v>
       </c>
       <c r="P2" t="n">
-        <v>333.0701519544188</v>
+        <v>333.0252636192853</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15292,28 +15421,28 @@
         <v>0.0743</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05771433908416274</v>
+        <v>-0.05526269190900112</v>
       </c>
       <c r="J3" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K3" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002999247971908314</v>
+        <v>0.002798431078725794</v>
       </c>
       <c r="M3" t="n">
-        <v>6.195818337586817</v>
+        <v>6.153742247090559</v>
       </c>
       <c r="N3" t="n">
-        <v>58.50391173031802</v>
+        <v>58.00369945688285</v>
       </c>
       <c r="O3" t="n">
-        <v>7.648784983925095</v>
+        <v>7.616015983234466</v>
       </c>
       <c r="P3" t="n">
-        <v>334.3049025397224</v>
+        <v>334.2768334466449</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -15374,28 +15503,28 @@
         <v>0.0709</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01291264048173052</v>
+        <v>-0.00992276273175211</v>
       </c>
       <c r="J4" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K4" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001215986864901986</v>
+        <v>7.30588058531767e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.779231353702874</v>
+        <v>6.733858296102229</v>
       </c>
       <c r="N4" t="n">
-        <v>72.44072063479099</v>
+        <v>71.82641620759924</v>
       </c>
       <c r="O4" t="n">
-        <v>8.511211466929428</v>
+        <v>8.47504667878586</v>
       </c>
       <c r="P4" t="n">
-        <v>332.3974395173944</v>
+        <v>332.3632252541491</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15452,28 +15581,28 @@
         <v>0.0713</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04855717834490456</v>
+        <v>-0.0397726720425085</v>
       </c>
       <c r="J5" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K5" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003045413778076322</v>
+        <v>0.002069778907288877</v>
       </c>
       <c r="M5" t="n">
-        <v>5.159776167499059</v>
+        <v>5.158983792237107</v>
       </c>
       <c r="N5" t="n">
-        <v>40.78216627394484</v>
+        <v>40.65079467743561</v>
       </c>
       <c r="O5" t="n">
-        <v>6.386091627431041</v>
+        <v>6.375797571867821</v>
       </c>
       <c r="P5" t="n">
-        <v>347.2024308842167</v>
+        <v>347.1018911562048</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15530,28 +15659,28 @@
         <v>0.055</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05949408901079498</v>
+        <v>-0.05413040835196976</v>
       </c>
       <c r="J6" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K6" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003861571942382458</v>
+        <v>0.003249729522430189</v>
       </c>
       <c r="M6" t="n">
-        <v>5.222277194865524</v>
+        <v>5.208159032027889</v>
       </c>
       <c r="N6" t="n">
-        <v>48.24335932727722</v>
+        <v>47.90105037775196</v>
       </c>
       <c r="O6" t="n">
-        <v>6.945743972194571</v>
+        <v>6.921058472354641</v>
       </c>
       <c r="P6" t="n">
-        <v>344.754336176848</v>
+        <v>344.6929443522072</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15608,28 +15737,28 @@
         <v>0.0525</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2798018808327709</v>
+        <v>-0.2752042276095669</v>
       </c>
       <c r="J7" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K7" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06423388784585216</v>
+        <v>0.06324351031294062</v>
       </c>
       <c r="M7" t="n">
-        <v>5.939843441935661</v>
+        <v>5.911654981002083</v>
       </c>
       <c r="N7" t="n">
-        <v>60.26132870544958</v>
+        <v>59.7921581327393</v>
       </c>
       <c r="O7" t="n">
-        <v>7.762817059898396</v>
+        <v>7.7325389189282</v>
       </c>
       <c r="P7" t="n">
-        <v>344.3778768467749</v>
+        <v>344.3252624254594</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15686,28 +15815,28 @@
         <v>0.0557</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2746791063899015</v>
+        <v>-0.2593869231023459</v>
       </c>
       <c r="J8" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K8" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07641956265213457</v>
+        <v>0.06891441160053213</v>
       </c>
       <c r="M8" t="n">
-        <v>5.231233261320979</v>
+        <v>5.264613157888526</v>
       </c>
       <c r="N8" t="n">
-        <v>48.17877672402707</v>
+        <v>48.45058116626129</v>
       </c>
       <c r="O8" t="n">
-        <v>6.941093337798237</v>
+        <v>6.960645168823167</v>
       </c>
       <c r="P8" t="n">
-        <v>350.5401884251374</v>
+        <v>350.3651615511219</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -15749,7 +15878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I335"/>
+  <dimension ref="A1:I338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31493,6 +31622,147 @@
         </is>
       </c>
     </row>
+    <row r="336">
+      <c r="A336" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:13:56+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>-45.862166468450425,170.74106477020771</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>-45.86278418094319,170.74120671433425</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>-45.86340245162597,170.74135334938185</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>-45.86397383562265,170.74174497244286</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>-45.86454581551876,170.74206161885115</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>-45.86512589163281,170.74239552797994</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>-45.86560097086749,170.74300426756002</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:14:01+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>-45.86216414690713,170.74108849109902</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>-45.86278253338577,170.74122354870053</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>-45.863401308445326,170.74136352098802</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>-45.86397224701177,170.74175235715447</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>-45.864542599803684,170.7420715505943</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>-45.86512281770227,170.7424036899782</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>-45.86559640887271,170.74301521807615</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:14:16+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>-45.86216484586692,170.74108134932547</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>-45.862783157460846,170.74121717204676</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>-45.86340360909545,170.74134305063018</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>-45.86397417982161,170.74174337242195</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-45.86454486972029,170.7420645399522</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>-45.8651298621255,170.74238498539754</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>-45.865598712910604,170.74300968751268</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0507/nzd0507.xlsx
+++ b/data/nzd0507/nzd0507.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I338"/>
+  <dimension ref="A1:I340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,72 @@
         <v>352.14</v>
       </c>
       <c r="I338" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>334.9</v>
+      </c>
+      <c r="C339" t="n">
+        <v>335.05</v>
+      </c>
+      <c r="D339" t="n">
+        <v>333.77</v>
+      </c>
+      <c r="E339" t="n">
+        <v>350.77</v>
+      </c>
+      <c r="F339" t="n">
+        <v>346.19</v>
+      </c>
+      <c r="G339" t="n">
+        <v>338.7</v>
+      </c>
+      <c r="H339" t="n">
+        <v>352.14</v>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>334.46</v>
+      </c>
+      <c r="C340" t="n">
+        <v>334.48</v>
+      </c>
+      <c r="D340" t="n">
+        <v>332.94</v>
+      </c>
+      <c r="E340" t="n">
+        <v>350.42</v>
+      </c>
+      <c r="F340" t="n">
+        <v>346.27</v>
+      </c>
+      <c r="G340" t="n">
+        <v>338.66</v>
+      </c>
+      <c r="H340" t="n">
+        <v>351.83</v>
+      </c>
+      <c r="I340" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11608,7 +11674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B356"/>
+  <dimension ref="A1:B358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15171,6 +15237,26 @@
       </c>
       <c r="B356" t="n">
         <v>0.23</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -15339,28 +15425,28 @@
         <v>0.082</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02575194040913379</v>
+        <v>-0.02308284375233199</v>
       </c>
       <c r="J2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K2" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0006514918946389781</v>
+        <v>0.0005293543288606983</v>
       </c>
       <c r="M2" t="n">
-        <v>5.727976413356041</v>
+        <v>5.706772294605464</v>
       </c>
       <c r="N2" t="n">
-        <v>53.53611833038721</v>
+        <v>53.251632506507</v>
       </c>
       <c r="O2" t="n">
-        <v>7.316838000829812</v>
+        <v>7.297371616308642</v>
       </c>
       <c r="P2" t="n">
-        <v>333.0252636192853</v>
+        <v>332.994349227753</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15421,28 +15507,28 @@
         <v>0.0743</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05526269190900112</v>
+        <v>-0.05303310081117026</v>
       </c>
       <c r="J3" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K3" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002798431078725794</v>
+        <v>0.002606826928851835</v>
       </c>
       <c r="M3" t="n">
-        <v>6.153742247090559</v>
+        <v>6.129164087108604</v>
       </c>
       <c r="N3" t="n">
-        <v>58.00369945688285</v>
+        <v>57.68472189125099</v>
       </c>
       <c r="O3" t="n">
-        <v>7.616015983234466</v>
+        <v>7.595045878153139</v>
       </c>
       <c r="P3" t="n">
-        <v>334.2768334466449</v>
+        <v>334.2512116041336</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -15503,28 +15589,28 @@
         <v>0.0709</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.00992276273175211</v>
+        <v>-0.008504342387860847</v>
       </c>
       <c r="J4" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K4" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L4" t="n">
-        <v>7.30588058531767e-05</v>
+        <v>5.428674225371743e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.733858296102229</v>
+        <v>6.701130332182334</v>
       </c>
       <c r="N4" t="n">
-        <v>71.82641620759924</v>
+        <v>71.41290251405039</v>
       </c>
       <c r="O4" t="n">
-        <v>8.47504667878586</v>
+        <v>8.450615510958382</v>
       </c>
       <c r="P4" t="n">
-        <v>332.3632252541491</v>
+        <v>332.346928153301</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15581,28 +15667,28 @@
         <v>0.0713</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0397726720425085</v>
+        <v>-0.03463478720843036</v>
       </c>
       <c r="J5" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K5" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002069778907288877</v>
+        <v>0.001583987363482642</v>
       </c>
       <c r="M5" t="n">
-        <v>5.158983792237107</v>
+        <v>5.154957356427012</v>
       </c>
       <c r="N5" t="n">
-        <v>40.65079467743561</v>
+        <v>40.53194470463906</v>
       </c>
       <c r="O5" t="n">
-        <v>6.375797571867821</v>
+        <v>6.366470348995514</v>
       </c>
       <c r="P5" t="n">
-        <v>347.1018911562048</v>
+        <v>347.0428420328533</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15659,28 +15745,28 @@
         <v>0.055</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05413040835196976</v>
+        <v>-0.05075486601611028</v>
       </c>
       <c r="J6" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K6" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003249729522430189</v>
+        <v>0.002888425801097938</v>
       </c>
       <c r="M6" t="n">
-        <v>5.208159032027889</v>
+        <v>5.197655139014204</v>
       </c>
       <c r="N6" t="n">
-        <v>47.90105037775196</v>
+        <v>47.67058506231227</v>
       </c>
       <c r="O6" t="n">
-        <v>6.921058472354641</v>
+        <v>6.904388826124458</v>
       </c>
       <c r="P6" t="n">
-        <v>344.6929443522072</v>
+        <v>344.6541476202009</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15737,28 +15823,28 @@
         <v>0.0525</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2752042276095669</v>
+        <v>-0.2732057639627429</v>
       </c>
       <c r="J7" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K7" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06324351031294062</v>
+        <v>0.06305213237614182</v>
       </c>
       <c r="M7" t="n">
-        <v>5.911654981002083</v>
+        <v>5.887354438568781</v>
       </c>
       <c r="N7" t="n">
-        <v>59.7921581327393</v>
+        <v>59.45767636538375</v>
       </c>
       <c r="O7" t="n">
-        <v>7.7325389189282</v>
+        <v>7.710880388475998</v>
       </c>
       <c r="P7" t="n">
-        <v>344.3252624254594</v>
+        <v>344.3022936427409</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15815,28 +15901,28 @@
         <v>0.0557</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2593869231023459</v>
+        <v>-0.24969045710331</v>
       </c>
       <c r="J8" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K8" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06891441160053213</v>
+        <v>0.0643485099900919</v>
       </c>
       <c r="M8" t="n">
-        <v>5.264613157888526</v>
+        <v>5.284371820300923</v>
       </c>
       <c r="N8" t="n">
-        <v>48.45058116626129</v>
+        <v>48.59505480274731</v>
       </c>
       <c r="O8" t="n">
-        <v>6.960645168823167</v>
+        <v>6.971015335139302</v>
       </c>
       <c r="P8" t="n">
-        <v>350.3651615511219</v>
+        <v>350.2537188392261</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -15878,7 +15964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I338"/>
+  <dimension ref="A1:I340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31763,6 +31849,100 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>-45.86216469608986,170.74108287970554</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>-45.862782221348105,170.74122673702738</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>-45.86340250878498,170.7413528408015</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>-45.86397417982161,170.74174337242195</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-45.86454486972029,170.7420645399522</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-45.8651298621255,170.74238498539754</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>-45.865598712910604,170.74300968751268</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:14:24+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>-45.86216524527232,170.74107726831195</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>-45.86278293279387,170.7412194676421</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>-45.8634036948339,170.74134228775966</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>-45.863975106511006,170.74173906467325</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>-45.864544567064776,170.7420654747045</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>-45.86513003289936,170.74238453195312</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>-45.86560014141397,170.74300625856307</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0507/nzd0507.xlsx
+++ b/data/nzd0507/nzd0507.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I340"/>
+  <dimension ref="A1:I342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11658,6 +11658,72 @@
         <v>351.83</v>
       </c>
       <c r="I340" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>335.17</v>
+      </c>
+      <c r="C341" t="n">
+        <v>335.29</v>
+      </c>
+      <c r="D341" t="n">
+        <v>333.73</v>
+      </c>
+      <c r="E341" t="n">
+        <v>351.48</v>
+      </c>
+      <c r="F341" t="n">
+        <v>346.81</v>
+      </c>
+      <c r="G341" t="n">
+        <v>338.86</v>
+      </c>
+      <c r="H341" t="n">
+        <v>351.42</v>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>335.33</v>
+      </c>
+      <c r="C342" t="n">
+        <v>335.87</v>
+      </c>
+      <c r="D342" t="n">
+        <v>334.68</v>
+      </c>
+      <c r="E342" t="n">
+        <v>352.79</v>
+      </c>
+      <c r="F342" t="n">
+        <v>348.97</v>
+      </c>
+      <c r="G342" t="n">
+        <v>339.14</v>
+      </c>
+      <c r="H342" t="n">
+        <v>352.34</v>
+      </c>
+      <c r="I342" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11674,7 +11740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B358"/>
+  <dimension ref="A1:B360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15257,6 +15323,26 @@
       </c>
       <c r="B358" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>
@@ -15425,28 +15511,28 @@
         <v>0.082</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02308284375233199</v>
+        <v>-0.01983962423680419</v>
       </c>
       <c r="J2" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005293543288606983</v>
+        <v>0.0003953174247260938</v>
       </c>
       <c r="M2" t="n">
-        <v>5.706772294605464</v>
+        <v>5.68851264047246</v>
       </c>
       <c r="N2" t="n">
-        <v>53.251632506507</v>
+        <v>52.98632937599175</v>
       </c>
       <c r="O2" t="n">
-        <v>7.297371616308642</v>
+        <v>7.27917092641681</v>
       </c>
       <c r="P2" t="n">
-        <v>332.994349227753</v>
+        <v>332.9566541821608</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15507,28 +15593,28 @@
         <v>0.0743</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05303310081117026</v>
+        <v>-0.04995145409159393</v>
       </c>
       <c r="J3" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K3" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002606826928851835</v>
+        <v>0.002338356264639518</v>
       </c>
       <c r="M3" t="n">
-        <v>6.129164087108604</v>
+        <v>6.109196341649534</v>
       </c>
       <c r="N3" t="n">
-        <v>57.68472189125099</v>
+        <v>57.39092462036436</v>
       </c>
       <c r="O3" t="n">
-        <v>7.595045878153139</v>
+        <v>7.575679812423725</v>
       </c>
       <c r="P3" t="n">
-        <v>334.2512116041336</v>
+        <v>334.2156676427768</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -15589,28 +15675,28 @@
         <v>0.0709</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.008504342387860847</v>
+        <v>-0.006176134615953728</v>
       </c>
       <c r="J4" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K4" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L4" t="n">
-        <v>5.428674225371743e-05</v>
+        <v>2.895420705750773e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.701130332182334</v>
+        <v>6.673434565632353</v>
       </c>
       <c r="N4" t="n">
-        <v>71.41290251405039</v>
+        <v>71.02048137918653</v>
       </c>
       <c r="O4" t="n">
-        <v>8.450615510958382</v>
+        <v>8.42736503179888</v>
       </c>
       <c r="P4" t="n">
-        <v>332.346928153301</v>
+        <v>332.3200696555544</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15667,28 +15753,28 @@
         <v>0.0713</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03463478720843036</v>
+        <v>-0.02791630975323004</v>
       </c>
       <c r="J5" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K5" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001583987363482642</v>
+        <v>0.001036144357185798</v>
       </c>
       <c r="M5" t="n">
-        <v>5.154957356427012</v>
+        <v>5.159247076938982</v>
       </c>
       <c r="N5" t="n">
-        <v>40.53194470463906</v>
+        <v>40.50604877291822</v>
       </c>
       <c r="O5" t="n">
-        <v>6.366470348995514</v>
+        <v>6.364436249418971</v>
       </c>
       <c r="P5" t="n">
-        <v>347.0428420328533</v>
+        <v>346.96535012292</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -15745,28 +15831,28 @@
         <v>0.055</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05075486601611028</v>
+        <v>-0.04561792338362534</v>
       </c>
       <c r="J6" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K6" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002888425801097938</v>
+        <v>0.002355287150241359</v>
       </c>
       <c r="M6" t="n">
-        <v>5.197655139014204</v>
+        <v>5.197544579275038</v>
       </c>
       <c r="N6" t="n">
-        <v>47.67058506231227</v>
+        <v>47.52010822242579</v>
       </c>
       <c r="O6" t="n">
-        <v>6.904388826124458</v>
+        <v>6.89348302546875</v>
       </c>
       <c r="P6" t="n">
-        <v>344.6541476202009</v>
+        <v>344.5948864605398</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -15823,28 +15909,28 @@
         <v>0.0525</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2732057639627429</v>
+        <v>-0.2708805281943615</v>
       </c>
       <c r="J7" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K7" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06305213237614182</v>
+        <v>0.06270034279532122</v>
       </c>
       <c r="M7" t="n">
-        <v>5.887354438568781</v>
+        <v>5.864971828129881</v>
       </c>
       <c r="N7" t="n">
-        <v>59.45767636538375</v>
+        <v>59.13416567297362</v>
       </c>
       <c r="O7" t="n">
-        <v>7.710880388475998</v>
+        <v>7.689874229984104</v>
       </c>
       <c r="P7" t="n">
-        <v>344.3022936427409</v>
+        <v>344.2754754178857</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -15901,28 +15987,28 @@
         <v>0.0557</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.24969045710331</v>
+        <v>-0.2403537713275062</v>
       </c>
       <c r="J8" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="K8" t="n">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0643485099900919</v>
+        <v>0.06008887760544956</v>
       </c>
       <c r="M8" t="n">
-        <v>5.284371820300923</v>
+        <v>5.302590255902949</v>
       </c>
       <c r="N8" t="n">
-        <v>48.59505480274731</v>
+        <v>48.71569853080486</v>
       </c>
       <c r="O8" t="n">
-        <v>6.971015335139302</v>
+        <v>6.979663210413871</v>
       </c>
       <c r="P8" t="n">
-        <v>350.2537188392261</v>
+        <v>350.1460364509065</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -15964,7 +16050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I340"/>
+  <dimension ref="A1:I342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31943,6 +32029,100 @@
         </is>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:14:25+00:00</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>-45.86216435909139,170.7410863230606</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>-45.86278192179186,170.74122979782112</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>-45.86340256594399,170.7413523322212</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>-45.863972299965475,170.74175211099742</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>-45.864542524139786,170.74207178428233</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-45.86512917903005,170.74238679917525</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-45.86560203072469,170.74300172350047</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-21 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>-45.862164159388556,170.74108836356734</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>-45.86278119786391,170.74123719473917</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>-45.863401208416974,170.74136441100353</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>-45.86396883149674,170.7417682342831</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>-45.86453435243623,170.74209702258912</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>-45.86512798361294,170.74238997328615</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>-45.865597791295485,170.74301189973812</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
